--- a/base_clinicas.xlsx
+++ b/base_clinicas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marya\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC5E77FB-EFFD-4B4C-B0BE-65C3BF4F8138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA01A959-0FF5-41CA-8ABA-4A2180EBC9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{76129DDB-9418-40FD-8B13-F10C04EA8F2F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
   <si>
     <t>Nombre</t>
   </si>
@@ -45,9 +45,6 @@
     <t>Estudio</t>
   </si>
   <si>
-    <t>]</t>
-  </si>
-  <si>
     <t>Centro Vision Tech</t>
   </si>
   <si>
@@ -70,31 +67,67 @@
   </si>
   <si>
     <t>Diagnóstico Premium</t>
+  </si>
+  <si>
+    <t>Direccion</t>
+  </si>
+  <si>
+    <t>Whatsapp</t>
+  </si>
+  <si>
+    <t>Redes Sociales</t>
+  </si>
+  <si>
+    <t>Av Victoria, Caracas</t>
+  </si>
+  <si>
+    <t>Av Libertador, Caracas</t>
+  </si>
+  <si>
+    <t>Avenida Enrique Tejera, Valencia</t>
+  </si>
+  <si>
+    <t>Centro Comercial Las Americas, Maracay</t>
+  </si>
+  <si>
+    <t>Avenida Municipal, Puerto La Cruz</t>
+  </si>
+  <si>
+    <t>OptiFree</t>
+  </si>
+  <si>
+    <t>Chuao, Caracas</t>
+  </si>
+  <si>
+    <t>IG @visiontech</t>
+  </si>
+  <si>
+    <t>IG @ocularsur</t>
+  </si>
+  <si>
+    <t>IG @oftexpress</t>
+  </si>
+  <si>
+    <t>FB @ojoshospital</t>
+  </si>
+  <si>
+    <t>IG @diagnospremium</t>
+  </si>
+  <si>
+    <t>FB @OptiFree</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFD4D4D4"/>
-      <name val="Courier New"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFDCDCDC"/>
-      <name val="Courier New"/>
-      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -117,16 +150,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -442,117 +472,182 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C65E88F9-5F68-4FD9-8CB4-AC1BC6B50965}">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.21875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" style="3"/>
-    <col min="3" max="3" width="16.77734375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="23.21875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" style="1"/>
+    <col min="3" max="3" width="16.77734375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="34.6640625" customWidth="1"/>
+    <col min="6" max="6" width="22.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="D1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1">
+        <v>150</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3">
-        <v>150</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2">
+        <v>123</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="B3" s="1">
+        <v>85</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="2">
+        <v>456</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3">
-        <v>85</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="B4" s="1">
+        <v>95</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="3">
-        <v>95</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="2">
+        <v>789</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="B5" s="1">
+        <v>120</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="3">
-        <v>120</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="2">
+        <v>101112</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="3">
+      <c r="B6" s="1">
         <v>140</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2">
+        <v>131415</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1">
+        <v>90</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="2">
+        <v>161718</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/base_clinicas.xlsx
+++ b/base_clinicas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marya\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA01A959-0FF5-41CA-8ABA-4A2180EBC9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39610C6F-F832-4496-9257-CA294AF63CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{76129DDB-9418-40FD-8B13-F10C04EA8F2F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
   <si>
     <t>Nombre</t>
   </si>
@@ -78,27 +78,9 @@
     <t>Redes Sociales</t>
   </si>
   <si>
-    <t>Av Victoria, Caracas</t>
-  </si>
-  <si>
-    <t>Av Libertador, Caracas</t>
-  </si>
-  <si>
-    <t>Avenida Enrique Tejera, Valencia</t>
-  </si>
-  <si>
-    <t>Centro Comercial Las Americas, Maracay</t>
-  </si>
-  <si>
-    <t>Avenida Municipal, Puerto La Cruz</t>
-  </si>
-  <si>
     <t>OptiFree</t>
   </si>
   <si>
-    <t>Chuao, Caracas</t>
-  </si>
-  <si>
     <t>IG @visiontech</t>
   </si>
   <si>
@@ -115,6 +97,33 @@
   </si>
   <si>
     <t>FB @OptiFree</t>
+  </si>
+  <si>
+    <t>Av Libertador, Caracas, Venezuela</t>
+  </si>
+  <si>
+    <t>Centro Comercial Las Americas, Maracay, Venezuela</t>
+  </si>
+  <si>
+    <t>Avenida Enrique Tejera, Valencia, Venezuela</t>
+  </si>
+  <si>
+    <t>Avenida Municipal, Puerto La Cruz, Venezuela</t>
+  </si>
+  <si>
+    <t>Chuao, Caracas, Venezuela</t>
+  </si>
+  <si>
+    <t>Clinisac</t>
+  </si>
+  <si>
+    <t>Av Maria Teresa Toro, Caracas, Venezuela</t>
+  </si>
+  <si>
+    <t>Los Palos Grandes, Caracas, Venezuela</t>
+  </si>
+  <si>
+    <t>IG @clinisac</t>
   </si>
 </sst>
 </file>
@@ -478,7 +487,7 @@
     <col min="1" max="1" width="23.21875" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.5546875" style="1"/>
     <col min="3" max="3" width="16.77734375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="34.6640625" customWidth="1"/>
+    <col min="4" max="4" width="46.44140625" customWidth="1"/>
     <col min="6" max="6" width="22.21875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -513,13 +522,13 @@
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E2" s="2">
         <v>123</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -533,13 +542,13 @@
         <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E3" s="2">
         <v>456</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -553,13 +562,13 @@
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E4" s="2">
         <v>789</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -573,13 +582,13 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E5" s="2">
         <v>101112</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -593,18 +602,18 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E6" s="2">
         <v>131415</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1">
         <v>90</v>
@@ -613,19 +622,36 @@
         <v>7</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E7" s="2">
         <v>161718</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="F8" s="1"/>
+      <c r="A8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="1">
+        <v>80</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="2">
+        <v>412</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
     </row>

--- a/base_clinicas.xlsx
+++ b/base_clinicas.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marya\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39610C6F-F832-4496-9257-CA294AF63CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7DD61BF-2C1F-42AA-9250-D01461A415D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{76129DDB-9418-40FD-8B13-F10C04EA8F2F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{76129DDB-9418-40FD-8B13-F10C04EA8F2F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Campo Visual" sheetId="1" r:id="rId1"/>
+    <sheet name="OCT Nervio Optico" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="21">
   <si>
     <t>Nombre</t>
   </si>
@@ -45,30 +46,6 @@
     <t>Estudio</t>
   </si>
   <si>
-    <t>Centro Vision Tech</t>
-  </si>
-  <si>
-    <t>Topografía</t>
-  </si>
-  <si>
-    <t>Clínica Ocular Sur</t>
-  </si>
-  <si>
-    <t>Oftalmo Express</t>
-  </si>
-  <si>
-    <t>Paquimetria</t>
-  </si>
-  <si>
-    <t>Hospital de Ojos</t>
-  </si>
-  <si>
-    <t>Oct Nervio optico</t>
-  </si>
-  <si>
-    <t>Diagnóstico Premium</t>
-  </si>
-  <si>
     <t>Direccion</t>
   </si>
   <si>
@@ -78,62 +55,87 @@
     <t>Redes Sociales</t>
   </si>
   <si>
-    <t>OptiFree</t>
-  </si>
-  <si>
-    <t>IG @visiontech</t>
-  </si>
-  <si>
-    <t>IG @ocularsur</t>
-  </si>
-  <si>
-    <t>IG @oftexpress</t>
-  </si>
-  <si>
-    <t>FB @ojoshospital</t>
-  </si>
-  <si>
-    <t>IG @diagnospremium</t>
-  </si>
-  <si>
-    <t>FB @OptiFree</t>
-  </si>
-  <si>
-    <t>Av Libertador, Caracas, Venezuela</t>
-  </si>
-  <si>
-    <t>Centro Comercial Las Americas, Maracay, Venezuela</t>
-  </si>
-  <si>
-    <t>Avenida Enrique Tejera, Valencia, Venezuela</t>
-  </si>
-  <si>
-    <t>Avenida Municipal, Puerto La Cruz, Venezuela</t>
-  </si>
-  <si>
-    <t>Chuao, Caracas, Venezuela</t>
-  </si>
-  <si>
     <t>Clinisac</t>
   </si>
   <si>
-    <t>Av Maria Teresa Toro, Caracas, Venezuela</t>
-  </si>
-  <si>
-    <t>Los Palos Grandes, Caracas, Venezuela</t>
-  </si>
-  <si>
-    <t>IG @clinisac</t>
+    <t>Nivel</t>
+  </si>
+  <si>
+    <t>Premium</t>
+  </si>
+  <si>
+    <t>Basic</t>
+  </si>
+  <si>
+    <t>VisionParaiso</t>
+  </si>
+  <si>
+    <t>Campo Visual</t>
+  </si>
+  <si>
+    <t>Avenida José Antonio Paéz, Centro Comercial Multiplaza Paraiso. Nivel Caracas.</t>
+  </si>
+  <si>
+    <t>Avenida Louis Braille, con Av Maria Teresa Toro, Caracas 1040, Distrito Capital</t>
+  </si>
+  <si>
+    <t>Centro Comercial, Caracas 1050, Distrito Capital</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/oftalmolaserve/?hl=es</t>
+  </si>
+  <si>
+    <t>Ofatlmolaser</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/clinisac/?hl=es</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/visionparaisooficial/?hl=es</t>
+  </si>
+  <si>
+    <t>OCT Nervio Optico</t>
+  </si>
+  <si>
+    <t>Precio</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="4"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -156,10 +158,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -167,8 +170,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -487,8 +512,10 @@
     <col min="1" max="1" width="23.21875" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.5546875" style="1"/>
     <col min="3" max="3" width="16.77734375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="46.44140625" customWidth="1"/>
-    <col min="6" max="6" width="22.21875" customWidth="1"/>
+    <col min="4" max="4" width="69.109375" customWidth="1"/>
+    <col min="5" max="5" width="20.77734375" style="8" customWidth="1"/>
+    <col min="6" max="6" width="47.21875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -502,156 +529,102 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>12</v>
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="2">
-        <v>123</v>
+        <v>11</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="6">
+        <v>4129789904</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="2">
-        <v>456</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="E3" s="7">
+        <v>4128095121</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="2">
-        <v>789</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>17</v>
+        <v>11</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="4">
+        <v>4128069601</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1">
-        <v>120</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="2">
-        <v>101112</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>18</v>
-      </c>
+      <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="1">
-        <v>140</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="2">
-        <v>131415</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1">
-        <v>90</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="2">
-        <v>161718</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="D7" s="2"/>
+      <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="1">
-        <v>80</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="2">
-        <v>412</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="D8" s="2"/>
+      <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
     </row>
@@ -676,6 +649,131 @@
       <c r="H12" s="1"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="https://wa.me/4129789904" xr:uid="{2AABE6F7-B799-4B05-A1EC-524436CC6CDB}"/>
+    <hyperlink ref="E3" r:id="rId2" display="https://www.google.com/search?client=opera&amp;q=clinisac&amp;sourceid=opera&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{BD5CADB4-00F7-43D3-B16E-BF8D4D2DE475}"/>
+    <hyperlink ref="E4" r:id="rId3" display="https://www.google.com/search?q=oftalmolaser&amp;client=opera&amp;hs=Grh&amp;sca_esv=a810b04456997408&amp;sxsrf=ANbL-n5KxxJO9IyZ3BSxlmqw6cfYutVyOg%3A1771879842837&amp;ei=or2caevaMoHcwN4P7eKKqQs&amp;biw=1482&amp;bih=696&amp;gs_ssp=eJzj4tVP1zc0rEgpKzQuSsozYLRSNaiwSDZKNLW0tDBOTbZMMzM1tTKosDRKTExKNE0xMDRMNEk2SfLiyU8rSczJzc9JLE4tAgCt7xTg&amp;oq=oftalmolas&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiCm9mdGFsbW9sYXMqAggAMgsQLhiABBjHARivATIFEAAYgAQyBRAAGIAEMgUQABiABDILEC4YgAQYxwEYrwEyBRAAGIAEMgUQABiABDIFEAAYgAQyBRAAGIAEMgUQABiABDIaEC4YgAQYxwEYrwEYlwUY3AQY3gQY4ATYAQFIoZQBUABY_H9wA3gBkAEAmAGaAaAB_wyqAQQwLjEzuAEByAEA-AEBmAIRoAKFIqgCFMICEBAuGIAEGMcBGCcYigUYrwHCAgoQIxiABBgnGIoFwgIQECMY8AUYgAQYJxjJAhiKBcICChAAGIAEGEMYigXCAh0QLhiABBjHARiKBRivARiXBRjcBBjeBBjgBNgBAcICBBAjGCfCAgoQIxjwBRgnGMkCwgIQEC4YgAQY0QMYxwEYJxiKBcICEBAuGIAEGNEDGEMYxwEYigXCAgsQABiABBixAxiDAcICERAuGIAEGLEDGNEDGIMBGMcBwgIOEC4YgAQYsQMYgwEYigXCAggQABiABBixA8ICBxAjGCcY6gLCAhYQABiABBhDGLQCGOcGGIoFGOoC2AEBwgIcEC4YgAQY0QMYQxi0AhjnBhjHARiKBRjqAtgBAcICEBAAGAMYtAIY6gIYjwHYAQHCAhAQLhgDGLQCGOoCGI8B2AEBwgIKEC4YgAQYJxiKBcICDhAAGIAEGLEDGIMBGIoFwgIQEAAYgAQYsQMYQxiDARiKBcICCxAAGIAEGLEDGMkDwgILEAAYgAQYkgMYigXCAhAQABiABBixAxhDGMkDGIoFwgILEAAYgAQYkgMYywGYAxnxBRoITNlKXQkCugYGCAEQARgUkgcIMy4xMy44LTGgB_OiAbIHBDAuMTO4B4MOwgcHMi05LjcuMcgHnQGACAA&amp;sclient=gws-wiz-serp" xr:uid="{2195D2AE-6AF9-41F6-8E73-E6153AC2A0BA}"/>
+    <hyperlink ref="F4" r:id="rId4" xr:uid="{9F8AC87D-BF73-476B-A4D2-80E0F0F1A6ED}"/>
+    <hyperlink ref="F3" r:id="rId5" xr:uid="{62811EB1-B5B8-44B7-A167-BEAB848F7D41}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56F9F951-127F-4592-B671-99CD8AF49B2E}">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.77734375" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" customWidth="1"/>
+    <col min="4" max="4" width="66.77734375" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" customWidth="1"/>
+    <col min="6" max="6" width="50.88671875" customWidth="1"/>
+    <col min="7" max="7" width="13.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1">
+        <v>100</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="6">
+        <v>4129789904</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1">
+        <v>80</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="7">
+        <v>4128095121</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="1">
+        <v>90</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="4">
+        <v>4128069601</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="https://wa.me/4129789904" xr:uid="{A31538CC-2760-4267-9258-8E74F1971C92}"/>
+    <hyperlink ref="E3" r:id="rId2" display="https://www.google.com/search?client=opera&amp;q=clinisac&amp;sourceid=opera&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{4961F142-CE30-466C-9A7B-875930DC11B5}"/>
+    <hyperlink ref="E4" r:id="rId3" display="https://www.google.com/search?q=oftalmolaser&amp;client=opera&amp;hs=Grh&amp;sca_esv=a810b04456997408&amp;sxsrf=ANbL-n5KxxJO9IyZ3BSxlmqw6cfYutVyOg%3A1771879842837&amp;ei=or2caevaMoHcwN4P7eKKqQs&amp;biw=1482&amp;bih=696&amp;gs_ssp=eJzj4tVP1zc0rEgpKzQuSsozYLRSNaiwSDZKNLW0tDBOTbZMMzM1tTKosDRKTExKNE0xMDRMNEk2SfLiyU8rSczJzc9JLE4tAgCt7xTg&amp;oq=oftalmolas&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiCm9mdGFsbW9sYXMqAggAMgsQLhiABBjHARivATIFEAAYgAQyBRAAGIAEMgUQABiABDILEC4YgAQYxwEYrwEyBRAAGIAEMgUQABiABDIFEAAYgAQyBRAAGIAEMgUQABiABDIaEC4YgAQYxwEYrwEYlwUY3AQY3gQY4ATYAQFIoZQBUABY_H9wA3gBkAEAmAGaAaAB_wyqAQQwLjEzuAEByAEA-AEBmAIRoAKFIqgCFMICEBAuGIAEGMcBGCcYigUYrwHCAgoQIxiABBgnGIoFwgIQECMY8AUYgAQYJxjJAhiKBcICChAAGIAEGEMYigXCAh0QLhiABBjHARiKBRivARiXBRjcBBjeBBjgBNgBAcICBBAjGCfCAgoQIxjwBRgnGMkCwgIQEC4YgAQY0QMYxwEYJxiKBcICEBAuGIAEGNEDGEMYxwEYigXCAgsQABiABBixAxiDAcICERAuGIAEGLEDGNEDGIMBGMcBwgIOEC4YgAQYsQMYgwEYigXCAggQABiABBixA8ICBxAjGCcY6gLCAhYQABiABBhDGLQCGOcGGIoFGOoC2AEBwgIcEC4YgAQY0QMYQxi0AhjnBhjHARiKBRjqAtgBAcICEBAAGAMYtAIY6gIYjwHYAQHCAhAQLhgDGLQCGOoCGI8B2AEBwgIKEC4YgAQYJxiKBcICDhAAGIAEGLEDGIMBGIoFwgIQEAAYgAQYsQMYQxiDARiKBcICCxAAGIAEGLEDGMkDwgILEAAYgAQYkgMYigXCAhAQABiABBixAxhDGMkDGIoFwgILEAAYgAQYkgMYywGYAxnxBRoITNlKXQkCugYGCAEQARgUkgcIMy4xMy44LTGgB_OiAbIHBDAuMTO4B4MOwgcHMi05LjcuMcgHnQGACAA&amp;sclient=gws-wiz-serp" xr:uid="{4376B349-647A-40A2-8C5C-DBFB1FFD375C}"/>
+    <hyperlink ref="F4" r:id="rId4" xr:uid="{B68AC2CD-7E7A-4A75-A91A-A5A8A1B5E1AB}"/>
+    <hyperlink ref="F3" r:id="rId5" xr:uid="{855FB59C-D5A0-43D3-B921-3040B62E023F}"/>
+    <hyperlink ref="F2" r:id="rId6" xr:uid="{08651FAC-CE18-4EA4-9CBB-13C5D98C478A}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/base_clinicas.xlsx
+++ b/base_clinicas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marya\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7DD61BF-2C1F-42AA-9250-D01461A415D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A75B4CDC-B10C-47E5-AC6E-09EA93100B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{76129DDB-9418-40FD-8B13-F10C04EA8F2F}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="24">
   <si>
     <t>Nombre</t>
   </si>
@@ -98,6 +98,15 @@
   </si>
   <si>
     <t>Precio</t>
+  </si>
+  <si>
+    <t>Avenida José Antonio Paéz, Centro Comercial Multiplaza Paraiso. Nivel Caracas, Caracas, Venezuela</t>
+  </si>
+  <si>
+    <t>Avenida Louis Braille, con Av Maria Teresa Toro, Caracas 1040, Distrito Capital, Caracas, Venezuela</t>
+  </si>
+  <si>
+    <t>Centro Comercial, Caracas 1050, Distrito Capital, Caracas, Venezuela</t>
   </si>
 </sst>
 </file>
@@ -665,9 +674,10 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.77734375" customWidth="1"/>
+    <col min="1" max="1" width="15.5546875" customWidth="1"/>
+    <col min="2" max="2" width="8.77734375" customWidth="1"/>
     <col min="3" max="3" width="20.109375" customWidth="1"/>
-    <col min="4" max="4" width="66.77734375" customWidth="1"/>
+    <col min="4" max="4" width="81" customWidth="1"/>
     <col min="5" max="5" width="14.33203125" customWidth="1"/>
     <col min="6" max="6" width="50.88671875" customWidth="1"/>
     <col min="7" max="7" width="13.5546875" customWidth="1"/>
@@ -707,7 +717,7 @@
         <v>19</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E2" s="6">
         <v>4129789904</v>
@@ -730,7 +740,7 @@
         <v>19</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E3" s="7">
         <v>4128095121</v>
@@ -753,7 +763,7 @@
         <v>19</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E4" s="4">
         <v>4128069601</v>

--- a/base_clinicas.xlsx
+++ b/base_clinicas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marya\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A75B4CDC-B10C-47E5-AC6E-09EA93100B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91816658-29EF-4BF3-9778-1758F1BE3BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{76129DDB-9418-40FD-8B13-F10C04EA8F2F}"/>
   </bookViews>
@@ -106,7 +106,7 @@
     <t>Avenida Louis Braille, con Av Maria Teresa Toro, Caracas 1040, Distrito Capital, Caracas, Venezuela</t>
   </si>
   <si>
-    <t>Centro Comercial, Caracas 1050, Distrito Capital, Caracas, Venezuela</t>
+    <t>Centro Comercial El Recreo, Caracas 1050, Distrito Capital, Caracas, Venezuela</t>
   </si>
 </sst>
 </file>

--- a/base_clinicas.xlsx
+++ b/base_clinicas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marya\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91816658-29EF-4BF3-9778-1758F1BE3BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0566CD-7DD7-4328-8A37-D9FDC4A4FA00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{76129DDB-9418-40FD-8B13-F10C04EA8F2F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{76129DDB-9418-40FD-8B13-F10C04EA8F2F}"/>
   </bookViews>
   <sheets>
     <sheet name="Campo Visual" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="21">
   <si>
     <t>Nombre</t>
   </si>
@@ -73,15 +73,6 @@
     <t>Campo Visual</t>
   </si>
   <si>
-    <t>Avenida José Antonio Paéz, Centro Comercial Multiplaza Paraiso. Nivel Caracas.</t>
-  </si>
-  <si>
-    <t>Avenida Louis Braille, con Av Maria Teresa Toro, Caracas 1040, Distrito Capital</t>
-  </si>
-  <si>
-    <t>Centro Comercial, Caracas 1050, Distrito Capital</t>
-  </si>
-  <si>
     <t>https://www.instagram.com/oftalmolaserve/?hl=es</t>
   </si>
   <si>
@@ -103,10 +94,10 @@
     <t>Avenida José Antonio Paéz, Centro Comercial Multiplaza Paraiso. Nivel Caracas, Caracas, Venezuela</t>
   </si>
   <si>
-    <t>Avenida Louis Braille, con Av Maria Teresa Toro, Caracas 1040, Distrito Capital, Caracas, Venezuela</t>
-  </si>
-  <si>
-    <t>Centro Comercial El Recreo, Caracas 1050, Distrito Capital, Caracas, Venezuela</t>
+    <t>Avenida Louis Braille con Av Maria Teresa Toro Distrito Capital, Caracas, Venezuela</t>
+  </si>
+  <si>
+    <t>Centro Comercial El Recreo, Distrito Capital, Caracas, Venezuela</t>
   </si>
 </sst>
 </file>
@@ -518,11 +509,11 @@
   <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.21875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" style="1"/>
+    <col min="1" max="1" width="18.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="16.77734375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="69.109375" customWidth="1"/>
-    <col min="5" max="5" width="20.77734375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="81" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" style="8" customWidth="1"/>
     <col min="6" max="6" width="47.21875" style="2" customWidth="1"/>
     <col min="7" max="7" width="11.5546875" style="2"/>
   </cols>
@@ -561,13 +552,13 @@
         <v>11</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E2" s="6">
         <v>4129789904</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>9</v>
@@ -584,13 +575,13 @@
         <v>11</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E3" s="7">
         <v>4128095121</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>8</v>
@@ -598,7 +589,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1">
         <v>70</v>
@@ -607,13 +598,13 @@
         <v>11</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E4" s="4">
         <v>4128069601</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>8</v>
@@ -688,7 +679,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -714,16 +705,16 @@
         <v>100</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E2" s="6">
         <v>4129789904</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>9</v>
@@ -737,16 +728,16 @@
         <v>80</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="E3" s="7">
         <v>4128095121</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>8</v>
@@ -754,22 +745,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1">
         <v>90</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E4" s="4">
         <v>4128069601</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>8</v>

--- a/base_clinicas.xlsx
+++ b/base_clinicas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marya\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0566CD-7DD7-4328-8A37-D9FDC4A4FA00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67147624-6C65-4B65-8DB4-35204CE2681B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{76129DDB-9418-40FD-8B13-F10C04EA8F2F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{76129DDB-9418-40FD-8B13-F10C04EA8F2F}"/>
   </bookViews>
   <sheets>
     <sheet name="Campo Visual" sheetId="1" r:id="rId1"/>
@@ -91,13 +91,13 @@
     <t>Precio</t>
   </si>
   <si>
-    <t>Avenida José Antonio Paéz, Centro Comercial Multiplaza Paraiso. Nivel Caracas, Caracas, Venezuela</t>
-  </si>
-  <si>
-    <t>Avenida Louis Braille con Av Maria Teresa Toro Distrito Capital, Caracas, Venezuela</t>
-  </si>
-  <si>
-    <t>Centro Comercial El Recreo, Distrito Capital, Caracas, Venezuela</t>
+    <t>Avenida José Antonio Paéz, Caracas, Venezuela</t>
+  </si>
+  <si>
+    <t>Avenida Louis Braille con Av Maria Teresa Toro, Caracas, Venezuela</t>
+  </si>
+  <si>
+    <t>Centro Comercial El Recreo, Caracas, Venezuela</t>
   </si>
 </sst>
 </file>

--- a/base_clinicas.xlsx
+++ b/base_clinicas.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marya\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67147624-6C65-4B65-8DB4-35204CE2681B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{226B2AC0-7C0A-4C31-B068-A96310B6C701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{76129DDB-9418-40FD-8B13-F10C04EA8F2F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{76129DDB-9418-40FD-8B13-F10C04EA8F2F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Campo Visual" sheetId="1" r:id="rId1"/>
-    <sheet name="OCT Nervio Optico" sheetId="2" r:id="rId2"/>
+    <sheet name="Base de datos 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="20">
   <si>
     <t>Nombre</t>
   </si>
@@ -86,9 +85,6 @@
   </si>
   <si>
     <t>OCT Nervio Optico</t>
-  </si>
-  <si>
-    <t>Precio</t>
   </si>
   <si>
     <t>Avenida José Antonio Paéz, Caracas, Venezuela</t>
@@ -552,7 +548,7 @@
         <v>11</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" s="6">
         <v>4129789904</v>
@@ -575,7 +571,7 @@
         <v>11</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3" s="7">
         <v>4128095121</v>
@@ -598,7 +594,7 @@
         <v>11</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4" s="4">
         <v>4128069601</v>
@@ -611,15 +607,73 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D5" s="2"/>
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1">
+        <v>100</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="6">
+        <v>4129789904</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D6" s="2"/>
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1">
+        <v>80</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="7">
+        <v>4128095121</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D7" s="2"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1">
+        <v>90</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="4">
+        <v>4128069601</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -655,125 +709,12 @@
     <hyperlink ref="E4" r:id="rId3" display="https://www.google.com/search?q=oftalmolaser&amp;client=opera&amp;hs=Grh&amp;sca_esv=a810b04456997408&amp;sxsrf=ANbL-n5KxxJO9IyZ3BSxlmqw6cfYutVyOg%3A1771879842837&amp;ei=or2caevaMoHcwN4P7eKKqQs&amp;biw=1482&amp;bih=696&amp;gs_ssp=eJzj4tVP1zc0rEgpKzQuSsozYLRSNaiwSDZKNLW0tDBOTbZMMzM1tTKosDRKTExKNE0xMDRMNEk2SfLiyU8rSczJzc9JLE4tAgCt7xTg&amp;oq=oftalmolas&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiCm9mdGFsbW9sYXMqAggAMgsQLhiABBjHARivATIFEAAYgAQyBRAAGIAEMgUQABiABDILEC4YgAQYxwEYrwEyBRAAGIAEMgUQABiABDIFEAAYgAQyBRAAGIAEMgUQABiABDIaEC4YgAQYxwEYrwEYlwUY3AQY3gQY4ATYAQFIoZQBUABY_H9wA3gBkAEAmAGaAaAB_wyqAQQwLjEzuAEByAEA-AEBmAIRoAKFIqgCFMICEBAuGIAEGMcBGCcYigUYrwHCAgoQIxiABBgnGIoFwgIQECMY8AUYgAQYJxjJAhiKBcICChAAGIAEGEMYigXCAh0QLhiABBjHARiKBRivARiXBRjcBBjeBBjgBNgBAcICBBAjGCfCAgoQIxjwBRgnGMkCwgIQEC4YgAQY0QMYxwEYJxiKBcICEBAuGIAEGNEDGEMYxwEYigXCAgsQABiABBixAxiDAcICERAuGIAEGLEDGNEDGIMBGMcBwgIOEC4YgAQYsQMYgwEYigXCAggQABiABBixA8ICBxAjGCcY6gLCAhYQABiABBhDGLQCGOcGGIoFGOoC2AEBwgIcEC4YgAQY0QMYQxi0AhjnBhjHARiKBRjqAtgBAcICEBAAGAMYtAIY6gIYjwHYAQHCAhAQLhgDGLQCGOoCGI8B2AEBwgIKEC4YgAQYJxiKBcICDhAAGIAEGLEDGIMBGIoFwgIQEAAYgAQYsQMYQxiDARiKBcICCxAAGIAEGLEDGMkDwgILEAAYgAQYkgMYigXCAhAQABiABBixAxhDGMkDGIoFwgILEAAYgAQYkgMYywGYAxnxBRoITNlKXQkCugYGCAEQARgUkgcIMy4xMy44LTGgB_OiAbIHBDAuMTO4B4MOwgcHMi05LjcuMcgHnQGACAA&amp;sclient=gws-wiz-serp" xr:uid="{2195D2AE-6AF9-41F6-8E73-E6153AC2A0BA}"/>
     <hyperlink ref="F4" r:id="rId4" xr:uid="{9F8AC87D-BF73-476B-A4D2-80E0F0F1A6ED}"/>
     <hyperlink ref="F3" r:id="rId5" xr:uid="{62811EB1-B5B8-44B7-A167-BEAB848F7D41}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56F9F951-127F-4592-B671-99CD8AF49B2E}">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="15.5546875" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="20.109375" customWidth="1"/>
-    <col min="4" max="4" width="81" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" customWidth="1"/>
-    <col min="6" max="6" width="50.88671875" customWidth="1"/>
-    <col min="7" max="7" width="13.5546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="1">
-        <v>100</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="6">
-        <v>4129789904</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1">
-        <v>80</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="7">
-        <v>4128095121</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="1">
-        <v>90</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="4">
-        <v>4128069601</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" display="https://wa.me/4129789904" xr:uid="{A31538CC-2760-4267-9258-8E74F1971C92}"/>
-    <hyperlink ref="E3" r:id="rId2" display="https://www.google.com/search?client=opera&amp;q=clinisac&amp;sourceid=opera&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{4961F142-CE30-466C-9A7B-875930DC11B5}"/>
-    <hyperlink ref="E4" r:id="rId3" display="https://www.google.com/search?q=oftalmolaser&amp;client=opera&amp;hs=Grh&amp;sca_esv=a810b04456997408&amp;sxsrf=ANbL-n5KxxJO9IyZ3BSxlmqw6cfYutVyOg%3A1771879842837&amp;ei=or2caevaMoHcwN4P7eKKqQs&amp;biw=1482&amp;bih=696&amp;gs_ssp=eJzj4tVP1zc0rEgpKzQuSsozYLRSNaiwSDZKNLW0tDBOTbZMMzM1tTKosDRKTExKNE0xMDRMNEk2SfLiyU8rSczJzc9JLE4tAgCt7xTg&amp;oq=oftalmolas&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiCm9mdGFsbW9sYXMqAggAMgsQLhiABBjHARivATIFEAAYgAQyBRAAGIAEMgUQABiABDILEC4YgAQYxwEYrwEyBRAAGIAEMgUQABiABDIFEAAYgAQyBRAAGIAEMgUQABiABDIaEC4YgAQYxwEYrwEYlwUY3AQY3gQY4ATYAQFIoZQBUABY_H9wA3gBkAEAmAGaAaAB_wyqAQQwLjEzuAEByAEA-AEBmAIRoAKFIqgCFMICEBAuGIAEGMcBGCcYigUYrwHCAgoQIxiABBgnGIoFwgIQECMY8AUYgAQYJxjJAhiKBcICChAAGIAEGEMYigXCAh0QLhiABBjHARiKBRivARiXBRjcBBjeBBjgBNgBAcICBBAjGCfCAgoQIxjwBRgnGMkCwgIQEC4YgAQY0QMYxwEYJxiKBcICEBAuGIAEGNEDGEMYxwEYigXCAgsQABiABBixAxiDAcICERAuGIAEGLEDGNEDGIMBGMcBwgIOEC4YgAQYsQMYgwEYigXCAggQABiABBixA8ICBxAjGCcY6gLCAhYQABiABBhDGLQCGOcGGIoFGOoC2AEBwgIcEC4YgAQY0QMYQxi0AhjnBhjHARiKBRjqAtgBAcICEBAAGAMYtAIY6gIYjwHYAQHCAhAQLhgDGLQCGOoCGI8B2AEBwgIKEC4YgAQYJxiKBcICDhAAGIAEGLEDGIMBGIoFwgIQEAAYgAQYsQMYQxiDARiKBcICCxAAGIAEGLEDGMkDwgILEAAYgAQYkgMYigXCAhAQABiABBixAxhDGMkDGIoFwgILEAAYgAQYkgMYywGYAxnxBRoITNlKXQkCugYGCAEQARgUkgcIMy4xMy44LTGgB_OiAbIHBDAuMTO4B4MOwgcHMi05LjcuMcgHnQGACAA&amp;sclient=gws-wiz-serp" xr:uid="{4376B349-647A-40A2-8C5C-DBFB1FFD375C}"/>
-    <hyperlink ref="F4" r:id="rId4" xr:uid="{B68AC2CD-7E7A-4A75-A91A-A5A8A1B5E1AB}"/>
-    <hyperlink ref="F3" r:id="rId5" xr:uid="{855FB59C-D5A0-43D3-B921-3040B62E023F}"/>
-    <hyperlink ref="F2" r:id="rId6" xr:uid="{08651FAC-CE18-4EA4-9CBB-13C5D98C478A}"/>
+    <hyperlink ref="E5" r:id="rId6" display="https://wa.me/4129789904" xr:uid="{F3B316F0-ACFD-4B57-A829-C2FA9285B233}"/>
+    <hyperlink ref="E6" r:id="rId7" display="https://www.google.com/search?client=opera&amp;q=clinisac&amp;sourceid=opera&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{8ABBAF8D-ED7A-4FE7-B1B6-844DAC100F0D}"/>
+    <hyperlink ref="E7" r:id="rId8" display="https://www.google.com/search?q=oftalmolaser&amp;client=opera&amp;hs=Grh&amp;sca_esv=a810b04456997408&amp;sxsrf=ANbL-n5KxxJO9IyZ3BSxlmqw6cfYutVyOg%3A1771879842837&amp;ei=or2caevaMoHcwN4P7eKKqQs&amp;biw=1482&amp;bih=696&amp;gs_ssp=eJzj4tVP1zc0rEgpKzQuSsozYLRSNaiwSDZKNLW0tDBOTbZMMzM1tTKosDRKTExKNE0xMDRMNEk2SfLiyU8rSczJzc9JLE4tAgCt7xTg&amp;oq=oftalmolas&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiCm9mdGFsbW9sYXMqAggAMgsQLhiABBjHARivATIFEAAYgAQyBRAAGIAEMgUQABiABDILEC4YgAQYxwEYrwEyBRAAGIAEMgUQABiABDIFEAAYgAQyBRAAGIAEMgUQABiABDIaEC4YgAQYxwEYrwEYlwUY3AQY3gQY4ATYAQFIoZQBUABY_H9wA3gBkAEAmAGaAaAB_wyqAQQwLjEzuAEByAEA-AEBmAIRoAKFIqgCFMICEBAuGIAEGMcBGCcYigUYrwHCAgoQIxiABBgnGIoFwgIQECMY8AUYgAQYJxjJAhiKBcICChAAGIAEGEMYigXCAh0QLhiABBjHARiKBRivARiXBRjcBBjeBBjgBNgBAcICBBAjGCfCAgoQIxjwBRgnGMkCwgIQEC4YgAQY0QMYxwEYJxiKBcICEBAuGIAEGNEDGEMYxwEYigXCAgsQABiABBixAxiDAcICERAuGIAEGLEDGNEDGIMBGMcBwgIOEC4YgAQYsQMYgwEYigXCAggQABiABBixA8ICBxAjGCcY6gLCAhYQABiABBhDGLQCGOcGGIoFGOoC2AEBwgIcEC4YgAQY0QMYQxi0AhjnBhjHARiKBRjqAtgBAcICEBAAGAMYtAIY6gIYjwHYAQHCAhAQLhgDGLQCGOoCGI8B2AEBwgIKEC4YgAQYJxiKBcICDhAAGIAEGLEDGIMBGIoFwgIQEAAYgAQYsQMYQxiDARiKBcICCxAAGIAEGLEDGMkDwgILEAAYgAQYkgMYigXCAhAQABiABBixAxhDGMkDGIoFwgILEAAYgAQYkgMYywGYAxnxBRoITNlKXQkCugYGCAEQARgUkgcIMy4xMy44LTGgB_OiAbIHBDAuMTO4B4MOwgcHMi05LjcuMcgHnQGACAA&amp;sclient=gws-wiz-serp" xr:uid="{76DE34A6-81C7-40B3-8815-9D5F6E1F162B}"/>
+    <hyperlink ref="F7" r:id="rId9" xr:uid="{AA245C2D-CCC1-4D2B-97E7-78536CA315B0}"/>
+    <hyperlink ref="F6" r:id="rId10" xr:uid="{B0BF1FE9-8710-4843-8A6E-274C841577C4}"/>
+    <hyperlink ref="F5" r:id="rId11" xr:uid="{6B42F8F3-501E-46B3-A234-73C38917EB4F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/base_clinicas.xlsx
+++ b/base_clinicas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marya\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{226B2AC0-7C0A-4C31-B068-A96310B6C701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72CE5288-A48D-4146-A2FE-83958FD1E49A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{76129DDB-9418-40FD-8B13-F10C04EA8F2F}"/>
   </bookViews>
@@ -75,9 +75,6 @@
     <t>https://www.instagram.com/oftalmolaserve/?hl=es</t>
   </si>
   <si>
-    <t>Ofatlmolaser</t>
-  </si>
-  <si>
     <t>https://www.instagram.com/clinisac/?hl=es</t>
   </si>
   <si>
@@ -94,6 +91,9 @@
   </si>
   <si>
     <t>Centro Comercial El Recreo, Caracas, Venezuela</t>
+  </si>
+  <si>
+    <t>Oftalmolaser</t>
   </si>
 </sst>
 </file>
@@ -548,13 +548,13 @@
         <v>11</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E2" s="6">
         <v>4129789904</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>9</v>
@@ -571,13 +571,13 @@
         <v>11</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" s="7">
         <v>4128095121</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>8</v>
@@ -585,7 +585,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B4" s="1">
         <v>70</v>
@@ -594,7 +594,7 @@
         <v>11</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" s="4">
         <v>4128069601</v>
@@ -614,16 +614,16 @@
         <v>100</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="E5" s="6">
         <v>4129789904</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>9</v>
@@ -637,16 +637,16 @@
         <v>80</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E6" s="7">
         <v>4128095121</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>8</v>
@@ -654,16 +654,16 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1">
         <v>90</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E7" s="4">
         <v>4128069601</v>

--- a/base_clinicas.xlsx
+++ b/base_clinicas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marya\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72CE5288-A48D-4146-A2FE-83958FD1E49A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D30EB8F-C4E4-4029-98AD-6CA9700623F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{76129DDB-9418-40FD-8B13-F10C04EA8F2F}"/>
   </bookViews>
@@ -57,15 +57,9 @@
     <t>Clinisac</t>
   </si>
   <si>
-    <t>Nivel</t>
-  </si>
-  <si>
     <t>Premium</t>
   </si>
   <si>
-    <t>Basic</t>
-  </si>
-  <si>
     <t>VisionParaiso</t>
   </si>
   <si>
@@ -94,6 +88,12 @@
   </si>
   <si>
     <t>Oftalmolaser</t>
+  </si>
+  <si>
+    <t>Plan</t>
+  </si>
+  <si>
+    <t>Basico</t>
   </si>
 </sst>
 </file>
@@ -534,30 +534,30 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1">
         <v>65</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E2" s="6">
         <v>4129789904</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -568,65 +568,65 @@
         <v>65</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E3" s="7">
         <v>4128095121</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B4" s="1">
         <v>70</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E4" s="4">
         <v>4128069601</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1">
         <v>100</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E5" s="6">
         <v>4129789904</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -637,42 +637,42 @@
         <v>80</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="E6" s="7">
         <v>4128095121</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B7" s="1">
         <v>90</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E7" s="4">
         <v>4128069601</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H7" s="1"/>
     </row>

--- a/base_clinicas.xlsx
+++ b/base_clinicas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marya\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D30EB8F-C4E4-4029-98AD-6CA9700623F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F170008D-E6B3-4F7B-AFB4-B887FE0D5A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{76129DDB-9418-40FD-8B13-F10C04EA8F2F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="22">
   <si>
     <t>Nombre</t>
   </si>
@@ -94,6 +94,12 @@
   </si>
   <si>
     <t>Basico</t>
+  </si>
+  <si>
+    <t>Clave Premium</t>
+  </si>
+  <si>
+    <t>ClinisacPremium26</t>
   </si>
 </sst>
 </file>
@@ -512,6 +518,7 @@
     <col min="5" max="5" width="16.6640625" style="8" customWidth="1"/>
     <col min="6" max="6" width="47.21875" style="2" customWidth="1"/>
     <col min="7" max="7" width="11.5546875" style="2"/>
+    <col min="8" max="8" width="17.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -536,6 +543,9 @@
       <c r="G1" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -574,13 +584,16 @@
         <v>15</v>
       </c>
       <c r="E3" s="7">
-        <v>4128095121</v>
+        <v>4127267157</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>7</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -643,13 +656,16 @@
         <v>15</v>
       </c>
       <c r="E6" s="7">
-        <v>4128095121</v>
+        <v>4127267157</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>7</v>
+      </c>
+      <c r="H6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">

--- a/base_clinicas.xlsx
+++ b/base_clinicas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marya\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F170008D-E6B3-4F7B-AFB4-B887FE0D5A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F34DEEC2-A3DB-4AFA-918A-69E8B7600258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{76129DDB-9418-40FD-8B13-F10C04EA8F2F}"/>
   </bookViews>
@@ -584,7 +584,7 @@
         <v>15</v>
       </c>
       <c r="E3" s="7">
-        <v>4127267157</v>
+        <v>584127267157</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>11</v>
@@ -656,7 +656,7 @@
         <v>15</v>
       </c>
       <c r="E6" s="7">
-        <v>4127267157</v>
+        <v>584127267157</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>11</v>

--- a/base_clinicas.xlsx
+++ b/base_clinicas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marya\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F34DEEC2-A3DB-4AFA-918A-69E8B7600258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3525DED8-A6B9-4A5A-B752-569D94B69CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{76129DDB-9418-40FD-8B13-F10C04EA8F2F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="23">
   <si>
     <t>Nombre</t>
   </si>
@@ -100,6 +100,9 @@
   </si>
   <si>
     <t>ClinisacPremium26</t>
+  </si>
+  <si>
+    <t>Pro</t>
   </si>
 </sst>
 </file>
@@ -616,7 +619,7 @@
         <v>10</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -688,7 +691,7 @@
         <v>10</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="H7" s="1"/>
     </row>

--- a/base_clinicas.xlsx
+++ b/base_clinicas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marya\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3525DED8-A6B9-4A5A-B752-569D94B69CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{782B97E9-F2A1-4184-8CFE-5719906A248E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{76129DDB-9418-40FD-8B13-F10C04EA8F2F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="37">
   <si>
     <t>Nombre</t>
   </si>
@@ -78,15 +78,6 @@
     <t>OCT Nervio Optico</t>
   </si>
   <si>
-    <t>Avenida José Antonio Paéz, Caracas, Venezuela</t>
-  </si>
-  <si>
-    <t>Avenida Louis Braille con Av Maria Teresa Toro, Caracas, Venezuela</t>
-  </si>
-  <si>
-    <t>Centro Comercial El Recreo, Caracas, Venezuela</t>
-  </si>
-  <si>
     <t>Oftalmolaser</t>
   </si>
   <si>
@@ -103,13 +94,64 @@
   </si>
   <si>
     <t>Pro</t>
+  </si>
+  <si>
+    <t>Fecha_Ref</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ciudad </t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>Caracas</t>
+  </si>
+  <si>
+    <t>Distrito Capital</t>
+  </si>
+  <si>
+    <t>Avenida José Antonio Paéz</t>
+  </si>
+  <si>
+    <t>Avenida Louis Braille con Av Maria Teresa Toro</t>
+  </si>
+  <si>
+    <t>Centro Comercial El Recreo</t>
+  </si>
+  <si>
+    <t>+584129789904</t>
+  </si>
+  <si>
+    <t>+584127267157</t>
+  </si>
+  <si>
+    <t>+584128069601</t>
+  </si>
+  <si>
+    <t>Salud Visual Margarita</t>
+  </si>
+  <si>
+    <t>Pampatar</t>
+  </si>
+  <si>
+    <t>Nueva Esparta</t>
+  </si>
+  <si>
+    <t>Av. Bolívar, Centro Empresarial AB. PB Local 1E</t>
+  </si>
+  <si>
+    <t>+584125090575</t>
+  </si>
+  <si>
+    <t>@saludvisualmargarita</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -145,6 +187,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -154,7 +218,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -162,12 +226,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -181,19 +269,46 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -511,46 +626,58 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C65E88F9-5F68-4FD9-8CB4-AC1BC6B50965}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.77734375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="81" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" style="8" customWidth="1"/>
-    <col min="6" max="6" width="47.21875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" style="2"/>
-    <col min="8" max="8" width="17.77734375" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="70.88671875" customWidth="1"/>
+    <col min="5" max="5" width="19.5546875" customWidth="1"/>
+    <col min="6" max="6" width="22.5546875" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" style="11" customWidth="1"/>
+    <col min="8" max="8" width="47.21875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="11.5546875" style="1"/>
+    <col min="10" max="10" width="17.77734375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.88671875" style="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1" s="18" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -560,20 +687,26 @@
       <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="6">
-        <v>4129789904</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -584,24 +717,30 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="7">
-        <v>584127267157</v>
-      </c>
-      <c r="F3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1">
         <v>70</v>
@@ -609,132 +748,195 @@
       <c r="C4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="4">
-        <v>4128069601</v>
-      </c>
-      <c r="F4" s="4" t="s">
+      <c r="D4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="I4" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="13">
+        <v>90</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="17">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B6" s="1">
         <v>100</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="6">
-        <v>4129789904</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="1">
-        <v>80</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="7">
-        <v>584127267157</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="4">
-        <v>4128069601</v>
-      </c>
-      <c r="F7" s="4" t="s">
+      <c r="D7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1">
+        <v>90</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="1"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D8" s="2"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
+      <c r="I8" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H12" s="1"/>
     </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H13" s="1"/>
+    </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E8" xr:uid="{C466BE21-399E-4176-B78B-69CA601F890D}">
+      <formula1>"Caracas, Barquisimeto, Merida, Pampatar, Valencia, Puerto La Cruz, Maturin, San Felipe, La Guaira, Puerto Ordaz, Lecheria, Maracaibo, Pampatar"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F8" xr:uid="{C2E8CB4C-771A-4283-9B7F-32BBCBB19C20}">
+      <formula1>"Amazonas, Anzoátegui, Apure, Aragua, Barinas, Bolívar, Carabobo, Cojedes, Delta Amacuro, Dependencias Federales, Distrito Capital, Falcón, Guárico, Lara, Mérida, Miranda, Monagas, Nueva Esparta, Portuguesa, Sucre, Táchira, Trujillo, Vargas, Yaracuy, Zulia"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I8" xr:uid="{6290E3E6-81D6-4A9A-9C87-DD48C7EB600D}">
+      <formula1>"Basico, Pro, Premium"</formula1>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" display="https://wa.me/4129789904" xr:uid="{2AABE6F7-B799-4B05-A1EC-524436CC6CDB}"/>
-    <hyperlink ref="E3" r:id="rId2" display="https://www.google.com/search?client=opera&amp;q=clinisac&amp;sourceid=opera&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{BD5CADB4-00F7-43D3-B16E-BF8D4D2DE475}"/>
-    <hyperlink ref="E4" r:id="rId3" display="https://www.google.com/search?q=oftalmolaser&amp;client=opera&amp;hs=Grh&amp;sca_esv=a810b04456997408&amp;sxsrf=ANbL-n5KxxJO9IyZ3BSxlmqw6cfYutVyOg%3A1771879842837&amp;ei=or2caevaMoHcwN4P7eKKqQs&amp;biw=1482&amp;bih=696&amp;gs_ssp=eJzj4tVP1zc0rEgpKzQuSsozYLRSNaiwSDZKNLW0tDBOTbZMMzM1tTKosDRKTExKNE0xMDRMNEk2SfLiyU8rSczJzc9JLE4tAgCt7xTg&amp;oq=oftalmolas&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiCm9mdGFsbW9sYXMqAggAMgsQLhiABBjHARivATIFEAAYgAQyBRAAGIAEMgUQABiABDILEC4YgAQYxwEYrwEyBRAAGIAEMgUQABiABDIFEAAYgAQyBRAAGIAEMgUQABiABDIaEC4YgAQYxwEYrwEYlwUY3AQY3gQY4ATYAQFIoZQBUABY_H9wA3gBkAEAmAGaAaAB_wyqAQQwLjEzuAEByAEA-AEBmAIRoAKFIqgCFMICEBAuGIAEGMcBGCcYigUYrwHCAgoQIxiABBgnGIoFwgIQECMY8AUYgAQYJxjJAhiKBcICChAAGIAEGEMYigXCAh0QLhiABBjHARiKBRivARiXBRjcBBjeBBjgBNgBAcICBBAjGCfCAgoQIxjwBRgnGMkCwgIQEC4YgAQY0QMYxwEYJxiKBcICEBAuGIAEGNEDGEMYxwEYigXCAgsQABiABBixAxiDAcICERAuGIAEGLEDGNEDGIMBGMcBwgIOEC4YgAQYsQMYgwEYigXCAggQABiABBixA8ICBxAjGCcY6gLCAhYQABiABBhDGLQCGOcGGIoFGOoC2AEBwgIcEC4YgAQY0QMYQxi0AhjnBhjHARiKBRjqAtgBAcICEBAAGAMYtAIY6gIYjwHYAQHCAhAQLhgDGLQCGOoCGI8B2AEBwgIKEC4YgAQYJxiKBcICDhAAGIAEGLEDGIMBGIoFwgIQEAAYgAQYsQMYQxiDARiKBcICCxAAGIAEGLEDGMkDwgILEAAYgAQYkgMYigXCAhAQABiABBixAxhDGMkDGIoFwgILEAAYgAQYkgMYywGYAxnxBRoITNlKXQkCugYGCAEQARgUkgcIMy4xMy44LTGgB_OiAbIHBDAuMTO4B4MOwgcHMi05LjcuMcgHnQGACAA&amp;sclient=gws-wiz-serp" xr:uid="{2195D2AE-6AF9-41F6-8E73-E6153AC2A0BA}"/>
-    <hyperlink ref="F4" r:id="rId4" xr:uid="{9F8AC87D-BF73-476B-A4D2-80E0F0F1A6ED}"/>
-    <hyperlink ref="F3" r:id="rId5" xr:uid="{62811EB1-B5B8-44B7-A167-BEAB848F7D41}"/>
-    <hyperlink ref="E5" r:id="rId6" display="https://wa.me/4129789904" xr:uid="{F3B316F0-ACFD-4B57-A829-C2FA9285B233}"/>
-    <hyperlink ref="E6" r:id="rId7" display="https://www.google.com/search?client=opera&amp;q=clinisac&amp;sourceid=opera&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{8ABBAF8D-ED7A-4FE7-B1B6-844DAC100F0D}"/>
-    <hyperlink ref="E7" r:id="rId8" display="https://www.google.com/search?q=oftalmolaser&amp;client=opera&amp;hs=Grh&amp;sca_esv=a810b04456997408&amp;sxsrf=ANbL-n5KxxJO9IyZ3BSxlmqw6cfYutVyOg%3A1771879842837&amp;ei=or2caevaMoHcwN4P7eKKqQs&amp;biw=1482&amp;bih=696&amp;gs_ssp=eJzj4tVP1zc0rEgpKzQuSsozYLRSNaiwSDZKNLW0tDBOTbZMMzM1tTKosDRKTExKNE0xMDRMNEk2SfLiyU8rSczJzc9JLE4tAgCt7xTg&amp;oq=oftalmolas&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiCm9mdGFsbW9sYXMqAggAMgsQLhiABBjHARivATIFEAAYgAQyBRAAGIAEMgUQABiABDILEC4YgAQYxwEYrwEyBRAAGIAEMgUQABiABDIFEAAYgAQyBRAAGIAEMgUQABiABDIaEC4YgAQYxwEYrwEYlwUY3AQY3gQY4ATYAQFIoZQBUABY_H9wA3gBkAEAmAGaAaAB_wyqAQQwLjEzuAEByAEA-AEBmAIRoAKFIqgCFMICEBAuGIAEGMcBGCcYigUYrwHCAgoQIxiABBgnGIoFwgIQECMY8AUYgAQYJxjJAhiKBcICChAAGIAEGEMYigXCAh0QLhiABBjHARiKBRivARiXBRjcBBjeBBjgBNgBAcICBBAjGCfCAgoQIxjwBRgnGMkCwgIQEC4YgAQY0QMYxwEYJxiKBcICEBAuGIAEGNEDGEMYxwEYigXCAgsQABiABBixAxiDAcICERAuGIAEGLEDGNEDGIMBGMcBwgIOEC4YgAQYsQMYgwEYigXCAggQABiABBixA8ICBxAjGCcY6gLCAhYQABiABBhDGLQCGOcGGIoFGOoC2AEBwgIcEC4YgAQY0QMYQxi0AhjnBhjHARiKBRjqAtgBAcICEBAAGAMYtAIY6gIYjwHYAQHCAhAQLhgDGLQCGOoCGI8B2AEBwgIKEC4YgAQYJxiKBcICDhAAGIAEGLEDGIMBGIoFwgIQEAAYgAQYsQMYQxiDARiKBcICCxAAGIAEGLEDGMkDwgILEAAYgAQYkgMYigXCAhAQABiABBixAxhDGMkDGIoFwgILEAAYgAQYkgMYywGYAxnxBRoITNlKXQkCugYGCAEQARgUkgcIMy4xMy44LTGgB_OiAbIHBDAuMTO4B4MOwgcHMi05LjcuMcgHnQGACAA&amp;sclient=gws-wiz-serp" xr:uid="{76DE34A6-81C7-40B3-8815-9D5F6E1F162B}"/>
-    <hyperlink ref="F7" r:id="rId9" xr:uid="{AA245C2D-CCC1-4D2B-97E7-78536CA315B0}"/>
-    <hyperlink ref="F6" r:id="rId10" xr:uid="{B0BF1FE9-8710-4843-8A6E-274C841577C4}"/>
-    <hyperlink ref="F5" r:id="rId11" xr:uid="{6B42F8F3-501E-46B3-A234-73C38917EB4F}"/>
+    <hyperlink ref="G2" r:id="rId1" display="https://wa.me/4129789904" xr:uid="{2AABE6F7-B799-4B05-A1EC-524436CC6CDB}"/>
+    <hyperlink ref="G3" r:id="rId2" display="https://www.google.com/search?client=opera&amp;q=clinisac&amp;sourceid=opera&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{BD5CADB4-00F7-43D3-B16E-BF8D4D2DE475}"/>
+    <hyperlink ref="G4" r:id="rId3" display="https://www.google.com/search?q=oftalmolaser&amp;client=opera&amp;hs=Grh&amp;sca_esv=a810b04456997408&amp;sxsrf=ANbL-n5KxxJO9IyZ3BSxlmqw6cfYutVyOg%3A1771879842837&amp;ei=or2caevaMoHcwN4P7eKKqQs&amp;biw=1482&amp;bih=696&amp;gs_ssp=eJzj4tVP1zc0rEgpKzQuSsozYLRSNaiwSDZKNLW0tDBOTbZMMzM1tTKosDRKTExKNE0xMDRMNEk2SfLiyU8rSczJzc9JLE4tAgCt7xTg&amp;oq=oftalmolas&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiCm9mdGFsbW9sYXMqAggAMgsQLhiABBjHARivATIFEAAYgAQyBRAAGIAEMgUQABiABDILEC4YgAQYxwEYrwEyBRAAGIAEMgUQABiABDIFEAAYgAQyBRAAGIAEMgUQABiABDIaEC4YgAQYxwEYrwEYlwUY3AQY3gQY4ATYAQFIoZQBUABY_H9wA3gBkAEAmAGaAaAB_wyqAQQwLjEzuAEByAEA-AEBmAIRoAKFIqgCFMICEBAuGIAEGMcBGCcYigUYrwHCAgoQIxiABBgnGIoFwgIQECMY8AUYgAQYJxjJAhiKBcICChAAGIAEGEMYigXCAh0QLhiABBjHARiKBRivARiXBRjcBBjeBBjgBNgBAcICBBAjGCfCAgoQIxjwBRgnGMkCwgIQEC4YgAQY0QMYxwEYJxiKBcICEBAuGIAEGNEDGEMYxwEYigXCAgsQABiABBixAxiDAcICERAuGIAEGLEDGNEDGIMBGMcBwgIOEC4YgAQYsQMYgwEYigXCAggQABiABBixA8ICBxAjGCcY6gLCAhYQABiABBhDGLQCGOcGGIoFGOoC2AEBwgIcEC4YgAQY0QMYQxi0AhjnBhjHARiKBRjqAtgBAcICEBAAGAMYtAIY6gIYjwHYAQHCAhAQLhgDGLQCGOoCGI8B2AEBwgIKEC4YgAQYJxiKBcICDhAAGIAEGLEDGIMBGIoFwgIQEAAYgAQYsQMYQxiDARiKBcICCxAAGIAEGLEDGMkDwgILEAAYgAQYkgMYigXCAhAQABiABBixAxhDGMkDGIoFwgILEAAYgAQYkgMYywGYAxnxBRoITNlKXQkCugYGCAEQARgUkgcIMy4xMy44LTGgB_OiAbIHBDAuMTO4B4MOwgcHMi05LjcuMcgHnQGACAA&amp;sclient=gws-wiz-serp" xr:uid="{2195D2AE-6AF9-41F6-8E73-E6153AC2A0BA}"/>
+    <hyperlink ref="H4" r:id="rId4" xr:uid="{9F8AC87D-BF73-476B-A4D2-80E0F0F1A6ED}"/>
+    <hyperlink ref="H3" r:id="rId5" xr:uid="{62811EB1-B5B8-44B7-A167-BEAB848F7D41}"/>
+    <hyperlink ref="G6" r:id="rId6" display="https://wa.me/4129789904" xr:uid="{F3B316F0-ACFD-4B57-A829-C2FA9285B233}"/>
+    <hyperlink ref="G7" r:id="rId7" display="https://www.google.com/search?client=opera&amp;q=clinisac&amp;sourceid=opera&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{8ABBAF8D-ED7A-4FE7-B1B6-844DAC100F0D}"/>
+    <hyperlink ref="G8" r:id="rId8" display="https://www.google.com/search?q=oftalmolaser&amp;client=opera&amp;hs=Grh&amp;sca_esv=a810b04456997408&amp;sxsrf=ANbL-n5KxxJO9IyZ3BSxlmqw6cfYutVyOg%3A1771879842837&amp;ei=or2caevaMoHcwN4P7eKKqQs&amp;biw=1482&amp;bih=696&amp;gs_ssp=eJzj4tVP1zc0rEgpKzQuSsozYLRSNaiwSDZKNLW0tDBOTbZMMzM1tTKosDRKTExKNE0xMDRMNEk2SfLiyU8rSczJzc9JLE4tAgCt7xTg&amp;oq=oftalmolas&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiCm9mdGFsbW9sYXMqAggAMgsQLhiABBjHARivATIFEAAYgAQyBRAAGIAEMgUQABiABDILEC4YgAQYxwEYrwEyBRAAGIAEMgUQABiABDIFEAAYgAQyBRAAGIAEMgUQABiABDIaEC4YgAQYxwEYrwEYlwUY3AQY3gQY4ATYAQFIoZQBUABY_H9wA3gBkAEAmAGaAaAB_wyqAQQwLjEzuAEByAEA-AEBmAIRoAKFIqgCFMICEBAuGIAEGMcBGCcYigUYrwHCAgoQIxiABBgnGIoFwgIQECMY8AUYgAQYJxjJAhiKBcICChAAGIAEGEMYigXCAh0QLhiABBjHARiKBRivARiXBRjcBBjeBBjgBNgBAcICBBAjGCfCAgoQIxjwBRgnGMkCwgIQEC4YgAQY0QMYxwEYJxiKBcICEBAuGIAEGNEDGEMYxwEYigXCAgsQABiABBixAxiDAcICERAuGIAEGLEDGNEDGIMBGMcBwgIOEC4YgAQYsQMYgwEYigXCAggQABiABBixA8ICBxAjGCcY6gLCAhYQABiABBhDGLQCGOcGGIoFGOoC2AEBwgIcEC4YgAQY0QMYQxi0AhjnBhjHARiKBRjqAtgBAcICEBAAGAMYtAIY6gIYjwHYAQHCAhAQLhgDGLQCGOoCGI8B2AEBwgIKEC4YgAQYJxiKBcICDhAAGIAEGLEDGIMBGIoFwgIQEAAYgAQYsQMYQxiDARiKBcICCxAAGIAEGLEDGMkDwgILEAAYgAQYkgMYigXCAhAQABiABBixAxhDGMkDGIoFwgILEAAYgAQYkgMYywGYAxnxBRoITNlKXQkCugYGCAEQARgUkgcIMy4xMy44LTGgB_OiAbIHBDAuMTO4B4MOwgcHMi05LjcuMcgHnQGACAA&amp;sclient=gws-wiz-serp" xr:uid="{76DE34A6-81C7-40B3-8815-9D5F6E1F162B}"/>
+    <hyperlink ref="H8" r:id="rId9" xr:uid="{AA245C2D-CCC1-4D2B-97E7-78536CA315B0}"/>
+    <hyperlink ref="H7" r:id="rId10" xr:uid="{B0BF1FE9-8710-4843-8A6E-274C841577C4}"/>
+    <hyperlink ref="H6" r:id="rId11" xr:uid="{6B42F8F3-501E-46B3-A234-73C38917EB4F}"/>
+    <hyperlink ref="H2" r:id="rId12" xr:uid="{1AA59B82-4408-461F-8F73-27E6A63FA189}"/>
+    <hyperlink ref="H5" r:id="rId13" display="https://www.instagram.com/saludvisualmargarita/" xr:uid="{0447C334-EABB-482F-9AEC-9058B38EF80B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="G2:G8" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/base_clinicas.xlsx
+++ b/base_clinicas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marya\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{782B97E9-F2A1-4184-8CFE-5719906A248E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F32CB740-BB35-4188-8AA3-46F29A175F9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{76129DDB-9418-40FD-8B13-F10C04EA8F2F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="41">
   <si>
     <t>Nombre</t>
   </si>
@@ -145,6 +145,18 @@
   </si>
   <si>
     <t>@saludvisualmargarita</t>
+  </si>
+  <si>
+    <t>Latitud</t>
+  </si>
+  <si>
+    <t>Longitud</t>
+  </si>
+  <si>
+    <t>10.48564</t>
+  </si>
+  <si>
+    <t>-66.90669</t>
   </si>
 </sst>
 </file>
@@ -293,22 +305,22 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -626,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C65E88F9-5F68-4FD9-8CB4-AC1BC6B50965}">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" style="1" customWidth="1"/>
@@ -639,10 +651,12 @@
     <col min="8" max="8" width="47.21875" style="2" customWidth="1"/>
     <col min="9" max="9" width="11.5546875" style="1"/>
     <col min="10" max="10" width="17.77734375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.88671875" style="17" customWidth="1"/>
+    <col min="11" max="11" width="18.88671875" style="16" customWidth="1"/>
+    <col min="12" max="12" width="14.44140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.109375" style="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -673,11 +687,17 @@
       <c r="J1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="17" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L1" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -706,7 +726,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -737,8 +757,14 @@
       <c r="J3" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L3" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -767,17 +793,17 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="1">
         <v>90</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="13" t="s">
         <v>34</v>
       </c>
       <c r="E5" s="5" t="s">
@@ -786,20 +812,20 @@
       <c r="F5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" s="15" t="s">
         <v>36</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K5" s="17">
+      <c r="K5" s="16">
         <v>46084</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -828,7 +854,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -859,8 +885,14 @@
       <c r="J7" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L7" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M7" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -889,22 +921,22 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="H13" s="1"/>
     </row>
   </sheetData>
@@ -935,8 +967,9 @@
     <hyperlink ref="H5" r:id="rId13" display="https://www.instagram.com/saludvisualmargarita/" xr:uid="{0447C334-EABB-482F-9AEC-9058B38EF80B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId14"/>
   <ignoredErrors>
-    <ignoredError sqref="G2:G8" numberStoredAsText="1"/>
+    <ignoredError sqref="G2:G8 L3:M3 L7:M7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/base_clinicas.xlsx
+++ b/base_clinicas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marya\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F32CB740-BB35-4188-8AA3-46F29A175F9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD322352-245C-461E-8E43-A7D93F9D80A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{76129DDB-9418-40FD-8B13-F10C04EA8F2F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="47">
   <si>
     <t>Nombre</t>
   </si>
@@ -157,6 +157,24 @@
   </si>
   <si>
     <t>-66.90669</t>
+  </si>
+  <si>
+    <t>10.48617</t>
+  </si>
+  <si>
+    <t>-66.93394</t>
+  </si>
+  <si>
+    <t>10.49118</t>
+  </si>
+  <si>
+    <t>-66.87733</t>
+  </si>
+  <si>
+    <t>10.98762</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -63.81753</t>
   </si>
 </sst>
 </file>
@@ -725,6 +743,12 @@
       <c r="I2" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="L2" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="18" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -792,6 +816,12 @@
       <c r="I4" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="L4" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="M4" s="18" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="5" spans="1:13" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
@@ -824,6 +854,12 @@
       <c r="K5" s="16">
         <v>46084</v>
       </c>
+      <c r="L5" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="M5" s="18" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -853,6 +889,12 @@
       <c r="I6" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="L6" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="M6" s="18" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -919,6 +961,12 @@
       </c>
       <c r="I8" s="1" t="s">
         <v>7</v>
+      </c>
+      <c r="L8" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="M8" s="18" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
@@ -969,7 +1017,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId14"/>
   <ignoredErrors>
-    <ignoredError sqref="G2:G8 L3:M3 L7:M7" numberStoredAsText="1"/>
+    <ignoredError sqref="G2:G8 L3:M3 L7:M7 L2:M2 L6:M6 L4:M4 L8:M8 L5:M5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/base_clinicas.xlsx
+++ b/base_clinicas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marya\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD322352-245C-461E-8E43-A7D93F9D80A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F2E164-CF28-4508-86EB-4BF7E46EA7F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{76129DDB-9418-40FD-8B13-F10C04EA8F2F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="48">
   <si>
     <t>Nombre</t>
   </si>
@@ -175,6 +175,9 @@
   </si>
   <si>
     <t xml:space="preserve"> -63.81753</t>
+  </si>
+  <si>
+    <t>Pampatar26</t>
   </si>
 </sst>
 </file>
@@ -849,7 +852,10 @@
         <v>36</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="K5" s="16">
         <v>46084</v>

--- a/base_clinicas.xlsx
+++ b/base_clinicas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marya\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marya\OneDrive\Desktop\BioData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A08B58-5557-4DFA-A76D-50E3272C07F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61F0D3EA-5A86-40BE-810E-41D3DA59A340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{76129DDB-9418-40FD-8B13-F10C04EA8F2F}"/>
   </bookViews>
@@ -403,10 +403,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1201,6 +1201,9 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="C14" s="1">
+        <v>75</v>
+      </c>
       <c r="D14" s="3" t="s">
         <v>68</v>
       </c>
@@ -1230,6 +1233,9 @@
       <c r="B15" s="1" t="s">
         <v>32</v>
       </c>
+      <c r="C15" s="1">
+        <v>75</v>
+      </c>
       <c r="D15" s="3" t="s">
         <v>68</v>
       </c>
@@ -1259,6 +1265,9 @@
       <c r="B16" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="C16" s="1">
+        <v>75</v>
+      </c>
       <c r="D16" s="3" t="s">
         <v>68</v>
       </c>
@@ -1288,6 +1297,9 @@
       <c r="B17" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="C17" s="1">
+        <v>75</v>
+      </c>
       <c r="D17" s="3" t="s">
         <v>68</v>
       </c>
@@ -1317,6 +1329,9 @@
       <c r="B18" s="1" t="s">
         <v>35</v>
       </c>
+      <c r="C18" s="1">
+        <v>100</v>
+      </c>
       <c r="D18" s="3" t="s">
         <v>68</v>
       </c>
@@ -1345,6 +1360,9 @@
       </c>
       <c r="B19" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="C19" s="1">
+        <v>75</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>68</v>
@@ -2694,7 +2712,7 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="G2:H7 G8:H13 G14:H19 G21:H25 G20:H20 I2:I31 G26:H32 G33:H37 G38:H38 G39:H43 I38:I43 I32:I37 G44:I44 G45:H49 I45:I49" numberStoredAsText="1"/>
+    <ignoredError sqref="G2:H7 G8:H13 G14:H19 G21:H25 G20:H20 I2:I19 G26:H32 G33:H37 G38:H38 G39:H43 I38:I43 I32:I37 G44:I44 G45:H49 I45:I49 I21:I26 I28:I31" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/base_clinicas.xlsx
+++ b/base_clinicas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marya\OneDrive\Desktop\BioData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61F0D3EA-5A86-40BE-810E-41D3DA59A340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F31A415-0CB7-44A5-A1CD-BAF47D541162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{76129DDB-9418-40FD-8B13-F10C04EA8F2F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="94">
   <si>
     <t>Nombre</t>
   </si>
@@ -75,9 +75,6 @@
     <t>ClinisacPremium26</t>
   </si>
   <si>
-    <t>Pro</t>
-  </si>
-  <si>
     <t>Fecha_Ref</t>
   </si>
   <si>
@@ -169,9 +166,6 @@
   </si>
   <si>
     <t>Zulia</t>
-  </si>
-  <si>
-    <t>Unidad Ocular de Occidente/COD Barquisimeto</t>
   </si>
   <si>
     <t>Carrera 17 Esquina Calle 19, Edificio Centro de Especialidades - Planta Baja, Barquisimeto.</t>
@@ -295,12 +289,45 @@
   <si>
     <t>584129453505</t>
   </si>
+  <si>
+    <t>COD Clinica Salud Visual</t>
+  </si>
+  <si>
+    <t>Clinica Oftalmologica IUMO</t>
+  </si>
+  <si>
+    <t>OCT Segmento Anterior</t>
+  </si>
+  <si>
+    <t>OCT Segmento Posterior</t>
+  </si>
+  <si>
+    <t>CEOVAL Centro Oftalmologico de Valencia</t>
+  </si>
+  <si>
+    <t>Av. Bolivar Norte, Edificio Torre Venezuela. Valencia. Estado Carabobo. Venezuela</t>
+  </si>
+  <si>
+    <t>10.22277</t>
+  </si>
+  <si>
+    <t>-68.01031</t>
+  </si>
+  <si>
+    <t>Calle San José, Urbanización La Trinidad, Caracas, Venezuela</t>
+  </si>
+  <si>
+    <t>-66.86359</t>
+  </si>
+  <si>
+    <t>10.43414</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -344,27 +371,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="4"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -380,7 +399,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -413,19 +432,47 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="12" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -743,15 +790,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4A4E827-F643-49B2-8A3A-4A373B325F16}">
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:L87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" style="17" customWidth="1"/>
     <col min="3" max="3" width="9" style="1" customWidth="1"/>
     <col min="4" max="4" width="63.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13.77734375" customWidth="1"/>
-    <col min="6" max="6" width="16.5546875" customWidth="1"/>
+    <col min="5" max="5" width="13.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5546875" style="1" customWidth="1"/>
     <col min="7" max="7" width="9.5546875" style="10" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.109375" style="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.6640625" style="10" customWidth="1"/>
@@ -764,26 +811,26 @@
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="G1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>3</v>
@@ -795,36 +842,36 @@
         <v>11</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="17" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="1">
         <v>65</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="G2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" s="15" t="s">
-        <v>69</v>
+      <c r="I2" s="24" t="s">
+        <v>67</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>5</v>
@@ -837,29 +884,29 @@
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>32</v>
+      <c r="B3" s="17" t="s">
+        <v>31</v>
       </c>
       <c r="C3" s="1">
         <v>65</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="G3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="15" t="s">
-        <v>69</v>
+      <c r="I3" s="24" t="s">
+        <v>67</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>5</v>
@@ -872,29 +919,29 @@
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>33</v>
+      <c r="B4" s="17" t="s">
+        <v>32</v>
       </c>
       <c r="C4" s="1">
         <v>65</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="G4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="15" t="s">
-        <v>69</v>
+      <c r="I4" s="24" t="s">
+        <v>67</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>5</v>
@@ -907,29 +954,29 @@
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>34</v>
+      <c r="B5" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="C5" s="1">
         <v>65</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="G5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="15" t="s">
-        <v>69</v>
+      <c r="I5" s="24" t="s">
+        <v>67</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>5</v>
@@ -942,29 +989,29 @@
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>35</v>
+      <c r="B6" s="17" t="s">
+        <v>34</v>
       </c>
       <c r="C6" s="1">
         <v>90</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="G6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>69</v>
+      <c r="I6" s="24" t="s">
+        <v>67</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>5</v>
@@ -977,29 +1024,29 @@
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="17" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="1">
         <v>65</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="G7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" s="15" t="s">
-        <v>69</v>
+      <c r="I7" s="24" t="s">
+        <v>67</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>5</v>
@@ -1010,28 +1057,28 @@
     </row>
     <row r="8" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="17" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="G8" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I8" s="16" t="s">
-        <v>71</v>
+      <c r="I8" s="24" t="s">
+        <v>69</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>10</v>
@@ -1039,28 +1086,28 @@
     </row>
     <row r="9" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>31</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="G9" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I9" s="16" t="s">
-        <v>71</v>
+      <c r="I9" s="24" t="s">
+        <v>69</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>10</v>
@@ -1068,31 +1115,31 @@
     </row>
     <row r="10" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>32</v>
       </c>
       <c r="C10" s="1">
         <v>65</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="G10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H10" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I10" s="16" t="s">
-        <v>71</v>
+      <c r="I10" s="24" t="s">
+        <v>69</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>10</v>
@@ -1100,31 +1147,31 @@
     </row>
     <row r="11" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="C11" s="1">
         <v>65</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="G11" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I11" s="16" t="s">
-        <v>71</v>
+      <c r="I11" s="24" t="s">
+        <v>69</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>10</v>
@@ -1132,31 +1179,31 @@
     </row>
     <row r="12" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" s="1" t="s">
         <v>35</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>34</v>
       </c>
       <c r="C12" s="1">
         <v>70</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="G12" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H12" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I12" s="16" t="s">
-        <v>71</v>
+      <c r="I12" s="24" t="s">
+        <v>69</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>10</v>
@@ -1164,31 +1211,31 @@
     </row>
     <row r="13" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="17" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="1">
         <v>65</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="G13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H13" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I13" s="16" t="s">
-        <v>71</v>
+      <c r="I13" s="24" t="s">
+        <v>69</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>10</v>
@@ -1198,218 +1245,218 @@
       <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="17" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="1">
         <v>75</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="G14" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="H14" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="14" t="s">
-        <v>72</v>
+      <c r="I14" s="24" t="s">
+        <v>70</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>32</v>
+      <c r="B15" s="17" t="s">
+        <v>31</v>
       </c>
       <c r="C15" s="1">
         <v>75</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="G15" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="H15" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="I15" s="14" t="s">
-        <v>72</v>
+      <c r="I15" s="24" t="s">
+        <v>70</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>33</v>
+      <c r="B16" s="17" t="s">
+        <v>32</v>
       </c>
       <c r="C16" s="1">
         <v>75</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="G16" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="14" t="s">
-        <v>72</v>
+      <c r="I16" s="24" t="s">
+        <v>70</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>34</v>
+      <c r="B17" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="C17" s="1">
         <v>75</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="G17" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="H17" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="14" t="s">
-        <v>72</v>
+      <c r="I17" s="24" t="s">
+        <v>70</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>35</v>
+      <c r="B18" s="17" t="s">
+        <v>34</v>
       </c>
       <c r="C18" s="1">
         <v>100</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="G18" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="H18" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="14" t="s">
-        <v>72</v>
+      <c r="I18" s="24" t="s">
+        <v>70</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="17" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="1">
         <v>75</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="G19" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="H19" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="14" t="s">
-        <v>72</v>
+      <c r="I19" s="24" t="s">
+        <v>70</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="17" t="s">
         <v>7</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G20" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>70</v>
+        <v>64</v>
+      </c>
+      <c r="I20" s="21" t="s">
+        <v>68</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>10</v>
@@ -1417,28 +1464,28 @@
     </row>
     <row r="21" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>31</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G21" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="I21" s="13" t="s">
-        <v>70</v>
+        <v>64</v>
+      </c>
+      <c r="I21" s="21" t="s">
+        <v>68</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>10</v>
@@ -1446,28 +1493,28 @@
     </row>
     <row r="22" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>32</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G22" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="I22" s="13" t="s">
-        <v>70</v>
+        <v>64</v>
+      </c>
+      <c r="I22" s="21" t="s">
+        <v>68</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>10</v>
@@ -1475,28 +1522,28 @@
     </row>
     <row r="23" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G23" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>70</v>
+        <v>64</v>
+      </c>
+      <c r="I23" s="21" t="s">
+        <v>68</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>10</v>
@@ -1504,28 +1551,28 @@
     </row>
     <row r="24" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>34</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G24" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="I24" s="13" t="s">
-        <v>70</v>
+        <v>64</v>
+      </c>
+      <c r="I24" s="21" t="s">
+        <v>68</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>10</v>
@@ -1533,28 +1580,28 @@
     </row>
     <row r="25" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="17" t="s">
         <v>6</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E25" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G25" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="I25" s="13" t="s">
-        <v>70</v>
+        <v>64</v>
+      </c>
+      <c r="I25" s="21" t="s">
+        <v>68</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>10</v>
@@ -1562,28 +1609,28 @@
     </row>
     <row r="26" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="17" t="s">
         <v>7</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="G26" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="I26" s="13" t="s">
         <v>73</v>
+      </c>
+      <c r="I26" s="21" t="s">
+        <v>71</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>10</v>
@@ -1591,28 +1638,28 @@
     </row>
     <row r="27" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>31</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="G27" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="I27" s="13" t="s">
         <v>73</v>
+      </c>
+      <c r="I27" s="21" t="s">
+        <v>71</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>10</v>
@@ -1620,28 +1667,28 @@
     </row>
     <row r="28" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>32</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="G28" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="I28" s="13" t="s">
         <v>73</v>
+      </c>
+      <c r="I28" s="21" t="s">
+        <v>71</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>10</v>
@@ -1649,28 +1696,28 @@
     </row>
     <row r="29" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="G29" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="I29" s="13" t="s">
         <v>73</v>
+      </c>
+      <c r="I29" s="21" t="s">
+        <v>71</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>10</v>
@@ -1678,28 +1725,28 @@
     </row>
     <row r="30" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>34</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E30" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="G30" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="I30" s="13" t="s">
         <v>73</v>
+      </c>
+      <c r="I30" s="21" t="s">
+        <v>71</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>10</v>
@@ -1707,202 +1754,202 @@
     </row>
     <row r="31" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="17" t="s">
         <v>6</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E31" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="G31" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="I31" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G31" s="7" t="s">
+      <c r="E32" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G32" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="H31" s="7" t="s">
+      <c r="H32" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="9" t="s">
+      <c r="I32" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D32" s="9" t="s">
+      <c r="F33" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="I32" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A33" s="9" t="s">
+      <c r="G33" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="I33" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D33" s="9" t="s">
+      <c r="F34" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="I33" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A34" s="9" t="s">
+      <c r="G34" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="I34" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D34" s="9" t="s">
+      <c r="F35" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="I34" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="9" t="s">
+      <c r="G35" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="I35" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D35" s="9" t="s">
+      <c r="F36" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="I35" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A36" s="9" t="s">
+      <c r="G36" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="I36" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D36" s="9" t="s">
+      <c r="F37" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="I36" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G37" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="I37" s="13" t="s">
-        <v>81</v>
+        <v>75</v>
+      </c>
+      <c r="I37" s="21" t="s">
+        <v>79</v>
       </c>
       <c r="J37" s="1" t="s">
         <v>10</v>
@@ -1910,86 +1957,87 @@
     </row>
     <row r="38" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F38" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>51</v>
-      </c>
       <c r="G38" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I38" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" s="13"/>
+      <c r="D39" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="H38" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="I38" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="9" t="s">
+      <c r="E39" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="F39" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="I39" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="J39" s="1" t="s">
+      <c r="G39" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="H39" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="I39" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="J39" s="13" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F40" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>51</v>
-      </c>
       <c r="G40" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="I40" s="13" t="s">
-        <v>73</v>
+        <v>77</v>
+      </c>
+      <c r="I40" s="21" t="s">
+        <v>71</v>
       </c>
       <c r="J40" s="1" t="s">
         <v>10</v>
@@ -1997,28 +2045,28 @@
     </row>
     <row r="41" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F41" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>51</v>
-      </c>
       <c r="G41" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="I41" s="13" t="s">
-        <v>73</v>
+        <v>77</v>
+      </c>
+      <c r="I41" s="21" t="s">
+        <v>71</v>
       </c>
       <c r="J41" s="1" t="s">
         <v>10</v>
@@ -2026,28 +2074,28 @@
     </row>
     <row r="42" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F42" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>51</v>
-      </c>
       <c r="G42" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="I42" s="13" t="s">
-        <v>73</v>
+        <v>77</v>
+      </c>
+      <c r="I42" s="21" t="s">
+        <v>71</v>
       </c>
       <c r="J42" s="1" t="s">
         <v>10</v>
@@ -2055,28 +2103,28 @@
     </row>
     <row r="43" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B43" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F43" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>51</v>
-      </c>
       <c r="G43" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="I43" s="13" t="s">
-        <v>73</v>
+        <v>77</v>
+      </c>
+      <c r="I43" s="21" t="s">
+        <v>71</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>10</v>
@@ -2084,28 +2132,28 @@
     </row>
     <row r="44" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F44" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F44" s="8" t="s">
-        <v>54</v>
-      </c>
       <c r="G44" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H44" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="I44" s="24" t="s">
         <v>82</v>
-      </c>
-      <c r="I44" s="12" t="s">
-        <v>84</v>
       </c>
       <c r="J44" s="1" t="s">
         <v>10</v>
@@ -2113,28 +2161,28 @@
     </row>
     <row r="45" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B45" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F45" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>54</v>
-      </c>
       <c r="G45" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H45" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="I45" s="24" t="s">
         <v>82</v>
-      </c>
-      <c r="I45" s="12" t="s">
-        <v>84</v>
       </c>
       <c r="J45" s="1" t="s">
         <v>10</v>
@@ -2142,28 +2190,28 @@
     </row>
     <row r="46" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B46" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F46" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>54</v>
-      </c>
       <c r="G46" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H46" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="I46" s="24" t="s">
         <v>82</v>
-      </c>
-      <c r="I46" s="12" t="s">
-        <v>84</v>
       </c>
       <c r="J46" s="1" t="s">
         <v>10</v>
@@ -2171,28 +2219,28 @@
     </row>
     <row r="47" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B47" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F47" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F47" s="8" t="s">
-        <v>54</v>
-      </c>
       <c r="G47" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H47" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="I47" s="24" t="s">
         <v>82</v>
-      </c>
-      <c r="I47" s="12" t="s">
-        <v>84</v>
       </c>
       <c r="J47" s="1" t="s">
         <v>10</v>
@@ -2200,28 +2248,28 @@
     </row>
     <row r="48" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B48" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F48" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F48" s="8" t="s">
-        <v>54</v>
-      </c>
       <c r="G48" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H48" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="I48" s="24" t="s">
         <v>82</v>
-      </c>
-      <c r="I48" s="12" t="s">
-        <v>84</v>
       </c>
       <c r="J48" s="1" t="s">
         <v>10</v>
@@ -2229,28 +2277,28 @@
     </row>
     <row r="49" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F49" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>54</v>
-      </c>
       <c r="G49" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H49" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="I49" s="24" t="s">
         <v>82</v>
-      </c>
-      <c r="I49" s="12" t="s">
-        <v>84</v>
       </c>
       <c r="J49" s="1" t="s">
         <v>10</v>
@@ -2258,445 +2306,913 @@
     </row>
     <row r="50" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B50" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>58</v>
-      </c>
       <c r="E50" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
+      <c r="I50" s="21"/>
     </row>
     <row r="51" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A51" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B51" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D51" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>58</v>
-      </c>
       <c r="E51" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G51" s="7"/>
       <c r="H51" s="7"/>
+      <c r="I51" s="21"/>
     </row>
     <row r="52" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D52" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>58</v>
-      </c>
       <c r="E52" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G52" s="7"/>
       <c r="H52" s="7"/>
+      <c r="I52" s="21"/>
     </row>
     <row r="53" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A53" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B53" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D53" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>58</v>
-      </c>
       <c r="E53" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G53" s="7"/>
       <c r="H53" s="7"/>
+      <c r="I53" s="21"/>
     </row>
     <row r="54" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B54" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D54" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>58</v>
-      </c>
       <c r="E54" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
+      <c r="I54" s="21"/>
     </row>
     <row r="55" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A55" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B55" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D55" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D55" s="9" t="s">
-        <v>58</v>
-      </c>
       <c r="E55" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G55" s="7"/>
       <c r="H55" s="7"/>
+      <c r="I55" s="21"/>
     </row>
     <row r="56" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E56" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>61</v>
-      </c>
       <c r="F56" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
+      <c r="I56" s="21"/>
     </row>
     <row r="57" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B57" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E57" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D57" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>61</v>
-      </c>
       <c r="F57" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="7"/>
+      <c r="I57" s="21"/>
     </row>
     <row r="58" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B58" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E58" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D58" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>61</v>
-      </c>
       <c r="F58" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G58" s="7"/>
       <c r="H58" s="7"/>
+      <c r="I58" s="21"/>
     </row>
     <row r="59" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B59" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E59" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D59" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>61</v>
-      </c>
       <c r="F59" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G59" s="7"/>
       <c r="H59" s="7"/>
+      <c r="I59" s="21"/>
     </row>
     <row r="60" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B60" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E60" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D60" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>61</v>
-      </c>
       <c r="F60" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
+      <c r="I60" s="21"/>
     </row>
     <row r="61" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B61" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E61" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D61" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>61</v>
-      </c>
       <c r="F61" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G61" s="7"/>
       <c r="H61" s="7"/>
+      <c r="I61" s="21"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B62" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E62" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D62" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E62" s="8" t="s">
+      <c r="F62" s="8" t="s">
         <v>21</v>
-      </c>
-      <c r="F62" s="8" t="s">
-        <v>22</v>
       </c>
       <c r="G62" s="7"/>
       <c r="H62" s="7"/>
+      <c r="I62" s="21"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B63" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E63" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D63" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E63" s="8" t="s">
+      <c r="F63" s="8" t="s">
         <v>21</v>
-      </c>
-      <c r="F63" s="8" t="s">
-        <v>22</v>
       </c>
       <c r="G63" s="7"/>
       <c r="H63" s="7"/>
+      <c r="I63" s="21"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B64" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E64" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D64" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E64" s="8" t="s">
+      <c r="F64" s="8" t="s">
         <v>21</v>
-      </c>
-      <c r="F64" s="8" t="s">
-        <v>22</v>
       </c>
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I64" s="21"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B65" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E65" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D65" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E65" s="8" t="s">
+      <c r="F65" s="8" t="s">
         <v>21</v>
-      </c>
-      <c r="F65" s="8" t="s">
-        <v>22</v>
       </c>
       <c r="G65" s="7"/>
       <c r="H65" s="7"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I65" s="21"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B66" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E66" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D66" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E66" s="8" t="s">
+      <c r="F66" s="8" t="s">
         <v>21</v>
-      </c>
-      <c r="F66" s="8" t="s">
-        <v>22</v>
       </c>
       <c r="G66" s="7"/>
       <c r="H66" s="7"/>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I66" s="21"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B67" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E67" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D67" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E67" s="8" t="s">
+      <c r="F67" s="8" t="s">
         <v>21</v>
-      </c>
-      <c r="F67" s="8" t="s">
-        <v>22</v>
       </c>
       <c r="G67" s="7"/>
       <c r="H67" s="7"/>
-    </row>
-    <row r="68" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="I67" s="21"/>
+    </row>
+    <row r="68" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A68" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E68" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F68" s="8" t="s">
         <v>17</v>
-      </c>
-      <c r="F68" s="8" t="s">
-        <v>18</v>
       </c>
       <c r="G68" s="7"/>
       <c r="H68" s="7"/>
-    </row>
-    <row r="69" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="I68" s="21"/>
+    </row>
+    <row r="69" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A69" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E69" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F69" s="8" t="s">
         <v>17</v>
-      </c>
-      <c r="F69" s="8" t="s">
-        <v>18</v>
       </c>
       <c r="G69" s="7"/>
       <c r="H69" s="7"/>
-    </row>
-    <row r="70" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="I69" s="21"/>
+    </row>
+    <row r="70" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A70" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E70" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F70" s="8" t="s">
         <v>17</v>
-      </c>
-      <c r="F70" s="8" t="s">
-        <v>18</v>
       </c>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
-    </row>
-    <row r="71" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="I70" s="21"/>
+    </row>
+    <row r="71" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A71" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E71" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F71" s="8" t="s">
         <v>17</v>
-      </c>
-      <c r="F71" s="8" t="s">
-        <v>18</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="7"/>
-    </row>
-    <row r="72" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="I71" s="21"/>
+    </row>
+    <row r="72" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A72" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E72" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F72" s="8" t="s">
         <v>17</v>
-      </c>
-      <c r="F72" s="8" t="s">
-        <v>18</v>
       </c>
       <c r="G72" s="7"/>
       <c r="H72" s="7"/>
-    </row>
-    <row r="73" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="I72" s="21"/>
+    </row>
+    <row r="73" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A73" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E73" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F73" s="8" t="s">
         <v>17</v>
-      </c>
-      <c r="F73" s="8" t="s">
-        <v>18</v>
       </c>
       <c r="G73" s="7"/>
       <c r="H73" s="7"/>
+      <c r="I73" s="21"/>
+    </row>
+    <row r="74" spans="1:10" s="18" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A74" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B74" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="17"/>
+      <c r="D74" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G74" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="H74" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="I74" s="26">
+        <v>584143052038</v>
+      </c>
+      <c r="J74" s="17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" s="18" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A75" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B75" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="17"/>
+      <c r="D75" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G75" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="H75" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="I75" s="26">
+        <v>584143052038</v>
+      </c>
+      <c r="J75" s="17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" s="18" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A76" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B76" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C76" s="17">
+        <v>100</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G76" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="H76" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="I76" s="26">
+        <v>584143052038</v>
+      </c>
+      <c r="J76" s="17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" s="18" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A77" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B77" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C77" s="17">
+        <v>90</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G77" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="H77" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="I77" s="26">
+        <v>584143052038</v>
+      </c>
+      <c r="J77" s="17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" s="18" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A78" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C78" s="17">
+        <v>160</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G78" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="H78" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="I78" s="26">
+        <v>584143052038</v>
+      </c>
+      <c r="J78" s="17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A79" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B79" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="1">
+        <v>90</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G79" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="H79" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="I79" s="26">
+        <v>584143052038</v>
+      </c>
+      <c r="J79" s="17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A80" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B80" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C80" s="1">
+        <v>160</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G80" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="H80" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="I80" s="26">
+        <v>584143052038</v>
+      </c>
+      <c r="J80" s="17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A81" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B81" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C81" s="1">
+        <v>160</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G81" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="H81" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="I81" s="26">
+        <v>584143052038</v>
+      </c>
+      <c r="J81" s="17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A82" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B82" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="1">
+        <v>50</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G82" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="H82" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="I82" s="22">
+        <v>584122368108</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A83" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B83" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="1">
+        <v>50</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G83" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="H83" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="I83" s="22">
+        <v>584122368108</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A84" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B84" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C84" s="1">
+        <v>25</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G84" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="H84" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="I84" s="22">
+        <v>584122368108</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A85" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B85" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C85" s="1">
+        <v>25</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G85" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="H85" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="I85" s="22">
+        <v>584122368108</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A86" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B86" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C86" s="1">
+        <v>60</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G86" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="H86" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="I86" s="22">
+        <v>584122368108</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A87" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B87" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="1">
+        <v>35</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="H87" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="I87" s="22">
+        <v>584122368108</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B67" xr:uid="{10248687-9DA8-448E-841B-6F108E56C305}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B67 B74:B79 B82:B87" xr:uid="{10248687-9DA8-448E-841B-6F108E56C305}">
       <mc:AlternateContent xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
         <mc:Choice Requires="x12ac">
           <x12ac:list>"OCT Nervio Optico, OCT Macula, Biometria, Topografia, Ecografia Ocular, Campo Visual"</x12ac:list>
@@ -2712,7 +3228,7 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="G2:H7 G8:H13 G14:H19 G21:H25 G20:H20 I2:I19 G26:H32 G33:H37 G38:H38 G39:H43 I38:I43 I32:I37 G44:I44 G45:H49 I45:I49 I21:I26 I28:I31" numberStoredAsText="1"/>
+    <ignoredError sqref="G2:H7 G8:H13 G14:H19 G21:H25 G20:H20 I2:I19 G26:H32 G33:H37 G38:H38 G39:H43 I38:I43 I32:I37 G44:I44 G45:H49 I45:I49 I21:I26 I28:I31 G82:H82 G83:H87 G74:H81" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>